--- a/E/SWACS.xlsx
+++ b/E/SWACS.xlsx
@@ -16,49 +16,58 @@
     <t/>
   </si>
   <si>
+    <t>20072581</t>
+  </si>
+  <si>
+    <t>IDM SEAWEED ORG 20G</t>
+  </si>
+  <si>
+    <t>SWACS</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20003915</t>
+  </si>
+  <si>
+    <t>IDM ABON SAPI 100GR</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20096677</t>
+  </si>
+  <si>
+    <t>IDM SOES COKELAT 80</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20038042</t>
   </si>
   <si>
     <t>TOLL MILK CANDY 120</t>
   </si>
   <si>
-    <t>SWACS</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20072581</t>
-  </si>
-  <si>
-    <t>IDM SEAWEED ORG 20G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES COKELAT 80</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>20118218</t>
+  </si>
+  <si>
+    <t>IDM MSK SLIM HTM 5S</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>20115472</t>
@@ -68,15 +77,6 @@
   </si>
   <si>
     <t>10</t>
-  </si>
-  <si>
-    <t>20118218</t>
-  </si>
-  <si>
-    <t>IDM MSK SLIM HTM 5S</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
 </sst>
 </file>
@@ -514,50 +514,50 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -574,10 +574,10 @@
         <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -594,10 +594,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -614,10 +614,10 @@
         <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/E/SWACS.xlsx
+++ b/E/SWACS.xlsx
@@ -16,21 +16,42 @@
     <t/>
   </si>
   <si>
+    <t>20038042</t>
+  </si>
+  <si>
+    <t>TOLL MILK CANDY 120</t>
+  </si>
+  <si>
+    <t>SWACS</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
     <t>20072581</t>
   </si>
   <si>
     <t>IDM SEAWEED ORG 20G</t>
   </si>
   <si>
-    <t>SWACS</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
+    <t>20096677</t>
+  </si>
+  <si>
+    <t>IDM SOES COKELAT 80</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>20003915</t>
   </si>
   <si>
@@ -40,25 +61,13 @@
     <t>2</t>
   </si>
   <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES COKELAT 80</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20038042</t>
-  </si>
-  <si>
-    <t>TOLL MILK CANDY 120</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>20115472</t>
+  </si>
+  <si>
+    <t>IDM MASK 4D HTM 4'S</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>20118218</t>
@@ -68,15 +77,6 @@
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>20115472</t>
-  </si>
-  <si>
-    <t>IDM MASK 4D HTM 4'S</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
 </sst>
 </file>
@@ -514,50 +514,50 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -574,10 +574,10 @@
         <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -594,10 +594,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -614,10 +614,10 @@
         <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/E/SWACS.xlsx
+++ b/E/SWACS.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t/>
   </si>
@@ -46,28 +46,10 @@
     <t>20096677</t>
   </si>
   <si>
-    <t>IDM SOES COKELAT 80</t>
+    <t>IDM SOES CKLT 80 G</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>20003915</t>
-  </si>
-  <si>
-    <t>IDM ABON SAPI 100GR</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20115472</t>
-  </si>
-  <si>
-    <t>IDM MASK 4D HTM 4'S</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
   <si>
     <t>20118218</t>
@@ -469,14 +451,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="3" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -577,46 +558,6 @@
         <v>5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/E/SWACS.xlsx
+++ b/E/SWACS.xlsx
@@ -11,54 +11,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t/>
   </si>
   <si>
-    <t>20038042</t>
-  </si>
-  <si>
-    <t>TOLL MILK CANDY 120</t>
+    <t>20118218</t>
+  </si>
+  <si>
+    <t>IDM MSK SLIM HTM 5S</t>
   </si>
   <si>
     <t>SWACS</t>
   </si>
   <si>
-    <t>4</t>
+    <t>9</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20072581</t>
-  </si>
-  <si>
-    <t>IDM SEAWEED ORG 20G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20096677</t>
-  </si>
-  <si>
-    <t>IDM SOES CKLT 80 G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20118218</t>
-  </si>
-  <si>
-    <t>IDM MSK SLIM HTM 5S</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
 </sst>
 </file>
@@ -451,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -501,66 +474,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
